--- a/docs/Plan_and_Progress/MOSAIC-SoC_Project_Plan_and_Progress.xlsx
+++ b/docs/Plan_and_Progress/MOSAIC-SoC_Project_Plan_and_Progress.xlsx
@@ -1563,7 +1563,7 @@
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>Not Started — needs PDK + SRAM macros</t>
+          <t>Done Aug 1 — Block A macro DRC/LVS clean (Magic 0, KLayout 0, Netgen "circuits match uniquely", XOR 0, antenna 0, IR 104 uV)</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress - macro re-hardened 2026-08-02 with the bug-31 fix: DRC/LVS/XOR/antenna all 0, max-cap 0, max-fanout 1, max-slew 591 vs the library's 4.0 ns. Top-level layout is the MPW integrator's</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Not Started — blocked on re-harden + slew/cap/fanout repair</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.68333333333333" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3286,6 +3286,342 @@
       <c r="H40" s="19" t="inlineStr">
         <is>
           <t>11/11 pass; total generator pytests now 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>Selectable platform blocks: soc.dma/debug/plic/spi_mode/multicore_timer/gpio_ao/ao_rv_timer/ao_fast_intr</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>MILOUDIAS</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>W31</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>Jul 29</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr">
+        <is>
+          <t>Jul 31</t>
+        </is>
+      </c>
+      <c r="H41" s="19" t="inlineStr">
+        <is>
+          <t>8 new schema knobs + template gates &amp; tie-offs; 71 tests in test_dma_selection.py; suite 636 green</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>GF180 area study: measured reduction 3.903 -&gt; 1.249 mm2 (-68%)</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>MILOUDIAS</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>W31</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>Jul 29</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>Jul 31</t>
+        </is>
+      </c>
+      <c r="H42" s="19" t="inlineStr">
+        <is>
+          <t>docs/area_study_gf180_min_soc.md 8c-8g; every step measured (yosys 0.62+slang, tt/25C/5v00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>Chipathon MPW Block A: 22-pin macro, routed GDS in 1117.5um slot</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>MILOUDIAS</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>W31</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>Jul 30</t>
+        </is>
+      </c>
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>Jul 31</t>
+        </is>
+      </c>
+      <c r="H43" s="19" t="inlineStr">
+        <is>
+          <t>mosaic_block_a.sv; die 1117.5x1117.5um=1.2488mm2; 0 routing DRC, 0 antenna; setup +20.67ns hold +0.075ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>GF180 library findings: no latch cell, unattributed SRAM blackboxes, unmapped tristates</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>MILOUDIAS</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>W31</t>
+        </is>
+      </c>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>Jul 30</t>
+        </is>
+      </c>
+      <c r="G44" s="20" t="inlineStr">
+        <is>
+          <t>Jul 31</t>
+        </is>
+      </c>
+      <c r="H44" s="19" t="inlineStr">
+        <is>
+          <t>hw/asic/gf180/{tc_clk,gf180_sram_blackbox,sram_wrapper}.sv - icgtp_1 ICG bind, (* blackbox *), bufz_4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>PDN core ring on Metal2/3 conflicts with router layer range</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>MILOUDIAS</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>W31</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>Jul 30</t>
+        </is>
+      </c>
+      <c r="G45" s="20" t="inlineStr">
+        <is>
+          <t>Jul 30</t>
+        </is>
+      </c>
+      <c r="H45" s="19" t="inlineStr">
+        <is>
+          <t>All detailed-routing violations were signal-to-VDD shorts on Metal3 along the ring; ring removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>DRC + LVS signoff on Block A GDS</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>MILOUDIAS</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>W31</t>
+        </is>
+      </c>
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>Aug 1</t>
+        </is>
+      </c>
+      <c r="G46" s="20" t="inlineStr">
+        <is>
+          <t>Aug 21</t>
+        </is>
+      </c>
+      <c r="H46" s="19" t="inlineStr">
+        <is>
+          <t>BLOCKER for submission. Magic/KLayout DRC + Netgen LVS never run on this GDS; status UNKNOWN not clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>Block A power delivery (PSM-0069) unresolved</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>MILOUDIAS</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>W31</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>Aug 1</t>
+        </is>
+      </c>
+      <c r="G47" s="20" t="inlineStr">
+        <is>
+          <t>Aug 21</t>
+        </is>
+      </c>
+      <c r="H47" s="19" t="inlineStr">
+        <is>
+          <t>PDN_CORE_RING:false leaves PSM without a power source; IR drop unanalysed</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>Confirm Block A pin contract with MPW integrator</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>MILOUDIAS</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>W31</t>
+        </is>
+      </c>
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>Aug 1</t>
+        </is>
+      </c>
+      <c r="G48" s="20" t="inlineStr">
+        <is>
+          <t>Aug 7</t>
+        </is>
+      </c>
+      <c r="H48" s="19" t="inlineStr">
+        <is>
+          <t>22 pins; bufz_4 QSPI drive is a placeholder; status_o[6:0] must be bonded (only observability, debug:false)</t>
         </is>
       </c>
     </row>
@@ -3957,7 +4293,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.68333333333333" defaultRowHeight="15" outlineLevelRow="7"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4016,22 +4352,22 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t>Week 29 Go/No-Go</t>
+          <t>Resolved Jul 31</t>
         </is>
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
-          <t>OpenRAM GF180 configs ready (4KB ~0.05mm² fits easily; 32KB needs check); switch to external SRAM / smaller mix if needed</t>
+          <t>Measured: GF180 SRAM macros are area-NEGATIVE below ~512 B (4x sram64x8 = 0.402 mm2 vs ~0.252 mm2 of flip-flops). Frozen part uses a 128 B flip-flop scratchpad, sram_kb: 0</t>
         </is>
       </c>
       <c r="E4" s="20" t="inlineStr">
         <is>
-          <t>Watching</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -4075,17 +4411,17 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>Week 26 (formal)</t>
+          <t>N/A for tapeout</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>FazyRV verified functionally in full-SoC sim; PicoRV32 fallback is now INTEGRATED and sim-verified (D-63) — swap is a one-line config change</t>
+          <t>FazyRV is not in the frozen Block A config (2x SERV). Remains sim-verified in the generator</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Watching</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -4102,17 +4438,17 @@
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>Week 31 (dry-run)</t>
+          <t>Resolved Aug 1</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>Drop to 25 MHz; 50 MHz was already conservative</t>
+          <t>Frozen part runs at 10 MHz (CLOCK_PERIOD 100) with +20.72 ns setup / +0.055 ns hold worst-corner, TNS 0 at all 9 corners. 50 MHz was dropped deliberately per reviewer advice</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>Watching</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -4194,6 +4530,114 @@
       <c r="E10" s="20" t="inlineStr">
         <is>
           <t>Watching</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Signed-off GDS predates the bug-31 fix</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Resolved Aug 2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Re-hardened with the fix in place; all decks clean at lower utilization (84.4%) than before</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Electrical rule violations not covered by any deck</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Before tapeout</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>max-cap 27-&gt;0, max-fanout 411-&gt;1, max-slew 2889-&gt;591 (measured against the library 4.0 ns rather than a tighter blanket default). Residual 591 needs per-net work: CTS_MAX_CAP and bufz_8 pad upsizing were both measured to make it worse</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Open, reduced</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Hand-modified vendored RTL untested</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Medium (hit)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>UART FIFOs cut 32-&gt;4 entries for area with no test. Closed by tb/mosaic_soc/run_uart.sh, which measures the depth directly and checks TX against the UART DPI log</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Mitigated</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Timing-annotated GLS unavailable with open tools</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Certain (hit)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Before tapeout</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PDK cell models use ifnone on edge-sensitive specify paths (illegal per IEEE 1364-2005 14.2.6); iverilog and CVC both reject, CVC then segfaults on the full netlist. Functional GLS passes; timing coverage rests on STA at 9 corners</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Open - needs commercial simulator</t>
         </is>
       </c>
     </row>
@@ -4391,9 +4835,21 @@
         </is>
       </c>
       <c r="C10" s="20" t="n"/>
-      <c r="D10" s="19" t="n"/>
-      <c r="E10" s="19" t="n"/>
-      <c r="F10" s="19" t="n"/>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>Area reduction 3.903 -&gt; 1.249 mm2 by measurement; 8 selectable platform knobs; Block A 22-pin macro wrapper; first routed GDS in the Chipathon slot</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>DRC/LVS not yet run</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>Run the full signoff decks</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -4407,9 +4863,21 @@
         </is>
       </c>
       <c r="C11" s="20" t="n"/>
-      <c r="D11" s="19" t="n"/>
-      <c r="E11" s="19" t="n"/>
-      <c r="F11" s="19" t="n"/>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>Block A re-hardened with the bug-31 fix: all decks clean, max-cap 27-&gt;0, max-fanout 411-&gt;1, max-slew 2889-&gt;591. RTL frozen + tagged rtl-freeze-blocka-v2. Gate-level simulation on the routed netlist passes (12 399 cycles vs RTL 12 400). UART bring-up test added</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>Timing-annotated GLS blocked: PDK models use illegal ifnone edge paths (IEEE 1364-2005 14.2.6) and CVC segfaults at this scale; 591 max-slew violations remain</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t>Per-net slew work; consider a commercial simulator for SDF GLS</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
